--- a/WIP/活頁簿1.xlsx
+++ b/WIP/活頁簿1.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Games\unciv-windows64\mods\Emperors-and-Deities\WIP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C392EB7-A1A7-4CCF-9BC4-56056C63B0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF7D46B-1A98-4490-B120-B6D5B01D154C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{C881A156-6EEB-4E61-80C2-9FE9DE8F1D18}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" firstSheet="2" activeTab="3" xr2:uid="{C881A156-6EEB-4E61-80C2-9FE9DE8F1D18}"/>
   </bookViews>
   <sheets>
     <sheet name="Techtree" sheetId="5" r:id="rId1"/>
     <sheet name="PTechtree" sheetId="15" r:id="rId2"/>
-    <sheet name="Event" sheetId="16" r:id="rId3"/>
-    <sheet name="BuildingOLD" sheetId="11" r:id="rId4"/>
-    <sheet name="UnitsOLD" sheetId="9" r:id="rId5"/>
-    <sheet name="Promotion" sheetId="8" r:id="rId6"/>
-    <sheet name="Civ DesignOLD(Out of Policy)" sheetId="6" r:id="rId7"/>
-    <sheet name="Civ DesignOLD(in Policy) chi" sheetId="13" r:id="rId8"/>
+    <sheet name="Promotion" sheetId="8" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="17" r:id="rId4"/>
+    <sheet name="Event" sheetId="16" r:id="rId5"/>
+    <sheet name="BuildingOLD" sheetId="11" r:id="rId6"/>
+    <sheet name="UnitsOLD" sheetId="9" r:id="rId7"/>
+    <sheet name="Civ DesignOLD(Out of Policy)" sheetId="6" r:id="rId8"/>
+    <sheet name="Civ DesignOLD(in Policy) chi" sheetId="13" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="820">
   <si>
     <t>Mining</t>
   </si>
@@ -3250,12 +3251,58 @@
     <t>Enact Policies</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
+  <si>
+    <t>Tutorial Events</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Building</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Event</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spark of Civilization</t>
+  </si>
+  <si>
+    <t>Into The Bronze Age</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sargon's Reign</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unify Mesopotamia</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>An House Divided</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Survive the Bronze Age Collapse</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Old Babylon</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sidequests</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3382,6 +3429,24 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -3485,7 +3550,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3636,6 +3701,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5231,6 +5305,724 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B53FB35-CF66-4CF1-8CCA-C87A13BE0A97}">
+  <dimension ref="A1:H57"/>
+  <sheetFormatPr defaultColWidth="16.25" defaultRowHeight="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="16.25" style="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="C1" s="40">
+        <v>2</v>
+      </c>
+      <c r="D1" s="40">
+        <v>3</v>
+      </c>
+      <c r="E1" s="40">
+        <v>4</v>
+      </c>
+      <c r="F1" s="40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>255</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="42">
+        <v>2</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="42">
+        <v>3</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="40" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="40" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="41" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>786</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>712</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="40" t="s">
+        <v>787</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="E11" s="40" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="40" t="s">
+        <v>788</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="40" t="s">
+        <v>790</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>211</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="40" t="s">
+        <v>789</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>236</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="E15" s="40" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="40" t="s">
+        <v>791</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="E16" s="40" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="40" t="s">
+        <v>792</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="40" t="s">
+        <v>793</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="40" t="s">
+        <v>794</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>217</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="40" t="s">
+        <v>779</v>
+      </c>
+      <c r="B20" s="40" t="s">
+        <v>780</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>781</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>782</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>783</v>
+      </c>
+      <c r="F20" s="40" t="s">
+        <v>784</v>
+      </c>
+      <c r="G20" s="40" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="40" t="s">
+        <v>332</v>
+      </c>
+      <c r="B24" s="43" t="s">
+        <v>203</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>471</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="C25" s="45" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="40" t="s">
+        <v>333</v>
+      </c>
+      <c r="B26" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="E26" s="40" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="D27" s="46" t="s">
+        <v>204</v>
+      </c>
+      <c r="E27" s="45" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="B29" s="41" t="s">
+        <v>260</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="G29" s="43"/>
+    </row>
+    <row r="30" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>298</v>
+      </c>
+      <c r="F30" s="43" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="D32" s="45" t="s">
+        <v>714</v>
+      </c>
+      <c r="E32" s="45" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="40" t="s">
+        <v>335</v>
+      </c>
+      <c r="B33" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="D33" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>795</v>
+      </c>
+      <c r="F33" s="40" t="s">
+        <v>796</v>
+      </c>
+      <c r="G33" s="45" t="s">
+        <v>718</v>
+      </c>
+      <c r="H33" s="45" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="40" t="s">
+        <v>336</v>
+      </c>
+      <c r="B34" s="40" t="s">
+        <v>324</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>341</v>
+      </c>
+      <c r="D34" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="E34" s="45" t="s">
+        <v>756</v>
+      </c>
+      <c r="F34" s="47" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="D35" s="40" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="B36" s="40" t="s">
+        <v>344</v>
+      </c>
+      <c r="C36" s="40" t="s">
+        <v>323</v>
+      </c>
+      <c r="D36" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="E36" s="40" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="40" t="s">
+        <v>200</v>
+      </c>
+      <c r="C37" s="40" t="s">
+        <v>201</v>
+      </c>
+      <c r="D37" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="E37" s="47" t="s">
+        <v>346</v>
+      </c>
+      <c r="F37" s="48" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="C38" s="47" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="C39" s="47" t="s">
+        <v>213</v>
+      </c>
+      <c r="D39" s="40" t="s">
+        <v>777</v>
+      </c>
+      <c r="E39" s="47" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="B40" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="C40" s="40" t="s">
+        <v>249</v>
+      </c>
+      <c r="D40" s="40" t="s">
+        <v>252</v>
+      </c>
+      <c r="E40" s="40" t="s">
+        <v>340</v>
+      </c>
+      <c r="F40" s="47" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="C41" s="40" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="40" t="s">
+        <v>339</v>
+      </c>
+      <c r="B42" s="40" t="s">
+        <v>347</v>
+      </c>
+      <c r="C42" s="40" t="s">
+        <v>348</v>
+      </c>
+      <c r="D42" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="E42" s="40" t="s">
+        <v>349</v>
+      </c>
+      <c r="F42" s="40" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="40" t="s">
+        <v>767</v>
+      </c>
+      <c r="B43" s="40" t="s">
+        <v>766</v>
+      </c>
+      <c r="C43" s="40" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="40" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="40" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="40" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="40" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="40" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="40" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="40" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="40" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="40" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="40" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="40" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11D303E-D867-461B-840C-08DCC82C77DC}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="23" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="23" style="51"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="52" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="53"/>
+    </row>
+    <row r="3" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="52" t="s">
+        <v>809</v>
+      </c>
+      <c r="B3" s="51" t="s">
+        <v>811</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>812</v>
+      </c>
+      <c r="D3" s="51" t="s">
+        <v>813</v>
+      </c>
+      <c r="F3" s="51" t="s">
+        <v>818</v>
+      </c>
+      <c r="H3" s="51" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="53"/>
+    </row>
+    <row r="5" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="53"/>
+      <c r="G5" s="51" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="53" t="s">
+        <v>816</v>
+      </c>
+      <c r="E6" s="51" t="s">
+        <v>814</v>
+      </c>
+      <c r="G6" s="51" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="52" t="s">
+        <v>810</v>
+      </c>
+      <c r="B7" s="51" t="s">
+        <v>811</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>812</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>813</v>
+      </c>
+      <c r="F7" s="51" t="s">
+        <v>818</v>
+      </c>
+      <c r="G7" s="51" t="s">
+        <v>819</v>
+      </c>
+      <c r="H7" s="51" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="51" t="s">
+        <v>815</v>
+      </c>
+      <c r="G8" s="51" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G9" s="51" t="s">
+        <v>819</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9EFEAA4-1654-490A-AB7D-56B611AFF5FD}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="45" defaultRowHeight="47.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5286,7 +6078,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F092E08-D523-4072-921C-A893C302A87B}">
   <dimension ref="A1:W12"/>
   <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="81.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5848,7 +6640,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C1F8F12-7BF1-4F36-BA5D-5C77B151C0AF}">
   <dimension ref="A1:AS18"/>
   <sheetFormatPr defaultColWidth="17.375" defaultRowHeight="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7042,626 +7834,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B53FB35-CF66-4CF1-8CCA-C87A13BE0A97}">
-  <dimension ref="A1:H57"/>
-  <sheetFormatPr defaultColWidth="16.25" defaultRowHeight="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="16384" width="16.25" style="40"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="B1" s="40" t="s">
-        <v>254</v>
-      </c>
-      <c r="C1" s="40">
-        <v>2</v>
-      </c>
-      <c r="D1" s="40">
-        <v>3</v>
-      </c>
-      <c r="E1" s="40">
-        <v>4</v>
-      </c>
-      <c r="F1" s="40">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
-        <v>255</v>
-      </c>
-      <c r="B2" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="C2" s="40" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="42">
-        <v>2</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>170</v>
-      </c>
-      <c r="C3" s="40" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42">
-        <v>3</v>
-      </c>
-      <c r="B4" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="40" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="40" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="41" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="B8" s="40" t="s">
-        <v>786</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="D8" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="E8" s="40" t="s">
-        <v>712</v>
-      </c>
-      <c r="F8" s="40" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="40" t="s">
-        <v>787</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="D9" s="40" t="s">
-        <v>164</v>
-      </c>
-      <c r="E9" s="40" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="40" t="s">
-        <v>246</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="D10" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="E10" s="40" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="40" t="s">
-        <v>245</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="40" t="s">
-        <v>247</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="D12" s="40" t="s">
-        <v>171</v>
-      </c>
-      <c r="E12" s="40" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="40" t="s">
-        <v>788</v>
-      </c>
-      <c r="C13" s="40" t="s">
-        <v>212</v>
-      </c>
-      <c r="D13" s="40" t="s">
-        <v>235</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="40" t="s">
-        <v>790</v>
-      </c>
-      <c r="C14" s="40" t="s">
-        <v>211</v>
-      </c>
-      <c r="D14" s="40" t="s">
-        <v>175</v>
-      </c>
-      <c r="E14" s="43" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="40" t="s">
-        <v>789</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>236</v>
-      </c>
-      <c r="D15" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="E15" s="40" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="40" t="s">
-        <v>791</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="D16" s="44" t="s">
-        <v>223</v>
-      </c>
-      <c r="E16" s="40" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="40" t="s">
-        <v>792</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="D17" s="40" t="s">
-        <v>222</v>
-      </c>
-      <c r="E17" s="40" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="40" t="s">
-        <v>793</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="D18" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="E18" s="40" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="40" t="s">
-        <v>794</v>
-      </c>
-      <c r="C19" s="40" t="s">
-        <v>180</v>
-      </c>
-      <c r="D19" s="40" t="s">
-        <v>217</v>
-      </c>
-      <c r="E19" s="40" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="40" t="s">
-        <v>779</v>
-      </c>
-      <c r="B20" s="40" t="s">
-        <v>780</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>781</v>
-      </c>
-      <c r="D20" s="40" t="s">
-        <v>782</v>
-      </c>
-      <c r="E20" s="40" t="s">
-        <v>783</v>
-      </c>
-      <c r="F20" s="40" t="s">
-        <v>784</v>
-      </c>
-      <c r="G20" s="40" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="40" t="s">
-        <v>332</v>
-      </c>
-      <c r="B24" s="43" t="s">
-        <v>203</v>
-      </c>
-      <c r="C24" s="40" t="s">
-        <v>471</v>
-      </c>
-      <c r="D24" s="44" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="C25" s="45" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="40" t="s">
-        <v>333</v>
-      </c>
-      <c r="B26" s="40" t="s">
-        <v>183</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>184</v>
-      </c>
-      <c r="D26" s="40" t="s">
-        <v>189</v>
-      </c>
-      <c r="E26" s="40" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="40" t="s">
-        <v>192</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>232</v>
-      </c>
-      <c r="D27" s="46" t="s">
-        <v>204</v>
-      </c>
-      <c r="E27" s="45" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="44" t="s">
-        <v>198</v>
-      </c>
-      <c r="C28" s="40" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="40" t="s">
-        <v>334</v>
-      </c>
-      <c r="B29" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>185</v>
-      </c>
-      <c r="G29" s="43"/>
-    </row>
-    <row r="30" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="C30" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="D30" s="43" t="s">
-        <v>205</v>
-      </c>
-      <c r="E30" s="43" t="s">
-        <v>298</v>
-      </c>
-      <c r="F30" s="43" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="43" t="s">
-        <v>206</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="40" t="s">
-        <v>193</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>231</v>
-      </c>
-      <c r="D32" s="45" t="s">
-        <v>714</v>
-      </c>
-      <c r="E32" s="45" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="B33" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>191</v>
-      </c>
-      <c r="D33" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="E33" s="40" t="s">
-        <v>795</v>
-      </c>
-      <c r="F33" s="40" t="s">
-        <v>796</v>
-      </c>
-      <c r="G33" s="45" t="s">
-        <v>718</v>
-      </c>
-      <c r="H33" s="45" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="40" t="s">
-        <v>336</v>
-      </c>
-      <c r="B34" s="40" t="s">
-        <v>324</v>
-      </c>
-      <c r="C34" s="40" t="s">
-        <v>341</v>
-      </c>
-      <c r="D34" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="E34" s="45" t="s">
-        <v>756</v>
-      </c>
-      <c r="F34" s="47" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="40" t="s">
-        <v>194</v>
-      </c>
-      <c r="C35" s="44" t="s">
-        <v>195</v>
-      </c>
-      <c r="D35" s="40" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="B36" s="40" t="s">
-        <v>344</v>
-      </c>
-      <c r="C36" s="40" t="s">
-        <v>323</v>
-      </c>
-      <c r="D36" s="40" t="s">
-        <v>250</v>
-      </c>
-      <c r="E36" s="40" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="C37" s="40" t="s">
-        <v>201</v>
-      </c>
-      <c r="D37" s="40" t="s">
-        <v>197</v>
-      </c>
-      <c r="E37" s="47" t="s">
-        <v>346</v>
-      </c>
-      <c r="F37" s="48" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="47" t="s">
-        <v>214</v>
-      </c>
-      <c r="C38" s="47" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C39" s="47" t="s">
-        <v>213</v>
-      </c>
-      <c r="D39" s="40" t="s">
-        <v>777</v>
-      </c>
-      <c r="E39" s="47" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="40" t="s">
-        <v>338</v>
-      </c>
-      <c r="B40" s="40" t="s">
-        <v>238</v>
-      </c>
-      <c r="C40" s="40" t="s">
-        <v>249</v>
-      </c>
-      <c r="D40" s="40" t="s">
-        <v>252</v>
-      </c>
-      <c r="E40" s="40" t="s">
-        <v>340</v>
-      </c>
-      <c r="F40" s="47" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="40" t="s">
-        <v>251</v>
-      </c>
-      <c r="C41" s="40" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="40" t="s">
-        <v>339</v>
-      </c>
-      <c r="B42" s="40" t="s">
-        <v>347</v>
-      </c>
-      <c r="C42" s="40" t="s">
-        <v>348</v>
-      </c>
-      <c r="D42" s="40" t="s">
-        <v>237</v>
-      </c>
-      <c r="E42" s="40" t="s">
-        <v>349</v>
-      </c>
-      <c r="F42" s="40" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="40" t="s">
-        <v>767</v>
-      </c>
-      <c r="B43" s="40" t="s">
-        <v>766</v>
-      </c>
-      <c r="C43" s="40" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="40" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="40" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="40" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="40" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="40" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="40" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="40" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="40" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="40" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="40" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="40" t="s">
-        <v>239</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBFFA452-D8B2-444A-A04B-53CFD30C9CB5}">
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="25.625" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7891,7 +8064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B65134C7-4BA5-4FC1-A5F8-F4E5303A0F6D}">
   <dimension ref="A1:P20"/>
   <sheetFormatPr defaultColWidth="22" defaultRowHeight="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
